--- a/research/traditional_assets/database/data/bulgaria/bulgaria_tobacco.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_tobacco.xlsx
@@ -587,26 +587,8 @@
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D2">
-        <v>-0.356</v>
-      </c>
-      <c r="G2">
-        <v>-2.525510204081633</v>
-      </c>
-      <c r="H2">
-        <v>-2.525510204081633</v>
-      </c>
-      <c r="I2">
-        <v>-3.26530612244898</v>
-      </c>
-      <c r="J2">
-        <v>-2.72797726685611</v>
-      </c>
       <c r="K2">
-        <v>0.132</v>
-      </c>
-      <c r="L2">
-        <v>0.336734693877551</v>
+        <v>-0.019</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +597,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +606,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.144</v>
+        <v>0.024</v>
       </c>
       <c r="V2">
-        <v>0.006288209606986899</v>
+        <v>0.0009448818897637796</v>
       </c>
       <c r="W2">
-        <v>0.007951807228915662</v>
+        <v>-0.001061452513966481</v>
       </c>
       <c r="X2">
-        <v>0.05580582226992591</v>
+        <v>0.1062486263580313</v>
       </c>
       <c r="Y2">
-        <v>-0.04785401504101024</v>
+        <v>-0.1073100788719978</v>
       </c>
       <c r="Z2">
-        <v>0.02503192848020434</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.06828653183956546</v>
+        <v>-0.0170464135021097</v>
       </c>
       <c r="AB2">
-        <v>0.05579283327542343</v>
+        <v>0.1062486263580313</v>
       </c>
       <c r="AC2">
-        <v>-0.1240793651149889</v>
+        <v>-0.123295039860141</v>
       </c>
       <c r="AD2">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.125</v>
+        <v>-0.024</v>
       </c>
       <c r="AH2">
-        <v>0.000829006501156246</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.001060327027177856</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.00548847420417124</v>
+        <v>-0.0009457755359394705</v>
       </c>
       <c r="AK2">
-        <v>-0.007032348804500703</v>
+        <v>-0.001439194051331255</v>
       </c>
       <c r="AL2">
-        <v>0.073</v>
+        <v>0.013</v>
       </c>
       <c r="AM2">
-        <v>-0.04300000000000001</v>
+        <v>0.009999999999999998</v>
       </c>
       <c r="AN2">
-        <v>-0.01919191919191919</v>
+        <v>-0</v>
       </c>
       <c r="AO2">
-        <v>-17.53424657534247</v>
+        <v>-46.61538461538461</v>
       </c>
       <c r="AP2">
-        <v>0.1262626262626262</v>
+        <v>0.06837606837606838</v>
       </c>
       <c r="AQ2">
-        <v>29.76744186046511</v>
+        <v>-60.60000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -715,26 +697,8 @@
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.356</v>
-      </c>
-      <c r="G3">
-        <v>-2.525510204081633</v>
-      </c>
-      <c r="H3">
-        <v>-2.525510204081633</v>
-      </c>
-      <c r="I3">
-        <v>-3.26530612244898</v>
-      </c>
-      <c r="J3">
-        <v>-2.72797726685611</v>
-      </c>
       <c r="K3">
-        <v>0.132</v>
-      </c>
-      <c r="L3">
-        <v>0.336734693877551</v>
+        <v>-0.019</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +707,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +716,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0.024</v>
+      </c>
+      <c r="V3">
+        <v>0.0009448818897637796</v>
+      </c>
+      <c r="W3">
+        <v>-0.001061452513966481</v>
+      </c>
+      <c r="X3">
+        <v>0.1062486263580313</v>
+      </c>
+      <c r="Y3">
+        <v>-0.1073100788719978</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>-0.0170464135021097</v>
+      </c>
+      <c r="AB3">
+        <v>0.1062486263580313</v>
+      </c>
+      <c r="AC3">
+        <v>-0.123295039860141</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>-0.024</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.0009457755359394705</v>
+      </c>
+      <c r="AK3">
+        <v>-0.001439194051331255</v>
+      </c>
+      <c r="AL3">
+        <v>0.013</v>
+      </c>
+      <c r="AM3">
+        <v>0.009999999999999998</v>
+      </c>
+      <c r="AN3">
         <v>-0</v>
       </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0.144</v>
-      </c>
-      <c r="V3">
-        <v>0.006288209606986899</v>
-      </c>
-      <c r="W3">
-        <v>0.007951807228915662</v>
-      </c>
-      <c r="X3">
-        <v>0.05580582226992591</v>
-      </c>
-      <c r="Y3">
-        <v>-0.04785401504101024</v>
-      </c>
-      <c r="Z3">
-        <v>0.02503192848020434</v>
-      </c>
-      <c r="AA3">
-        <v>-0.06828653183956546</v>
-      </c>
-      <c r="AB3">
-        <v>0.05579283327542343</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1240793651149889</v>
-      </c>
-      <c r="AD3">
-        <v>0.019</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0.019</v>
-      </c>
-      <c r="AG3">
-        <v>-0.125</v>
-      </c>
-      <c r="AH3">
-        <v>0.000829006501156246</v>
-      </c>
-      <c r="AI3">
-        <v>0.001060327027177856</v>
-      </c>
-      <c r="AJ3">
-        <v>-0.00548847420417124</v>
-      </c>
-      <c r="AK3">
-        <v>-0.007032348804500703</v>
-      </c>
-      <c r="AL3">
-        <v>0.073</v>
-      </c>
-      <c r="AM3">
-        <v>-0.04300000000000001</v>
-      </c>
-      <c r="AN3">
-        <v>-0.01919191919191919</v>
-      </c>
       <c r="AO3">
-        <v>-17.53424657534247</v>
+        <v>-46.61538461538461</v>
       </c>
       <c r="AP3">
-        <v>0.1262626262626262</v>
+        <v>0.06837606837606838</v>
       </c>
       <c r="AQ3">
-        <v>29.76744186046511</v>
+        <v>-60.60000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bulgaria/bulgaria_tobacco.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_tobacco.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,8 +587,29 @@
           <t>Tobacco</t>
         </is>
       </c>
+      <c r="D2">
+        <v>-0.203</v>
+      </c>
+      <c r="E2">
+        <v>-0.00298</v>
+      </c>
+      <c r="G2">
+        <v>0.034967919340055</v>
+      </c>
+      <c r="H2">
+        <v>0.034967919340055</v>
+      </c>
+      <c r="I2">
+        <v>-0.01118240146654446</v>
+      </c>
+      <c r="J2">
+        <v>-0.007879212830574411</v>
+      </c>
       <c r="K2">
-        <v>-0.019</v>
+        <v>19.242</v>
+      </c>
+      <c r="L2">
+        <v>0.1763703024747938</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -597,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -606,37 +627,25 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.024</v>
+        <v>0.016</v>
       </c>
       <c r="V2">
-        <v>0.0009448818897637796</v>
-      </c>
-      <c r="W2">
-        <v>-0.001061452513966481</v>
+        <v>0.0002527646129541864</v>
       </c>
       <c r="X2">
-        <v>0.1062486263580313</v>
-      </c>
-      <c r="Y2">
-        <v>-0.1073100788719978</v>
+        <v>0.07746242707851946</v>
       </c>
       <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>-0.0170464135021097</v>
+        <v>7.87157287157287</v>
       </c>
       <c r="AB2">
-        <v>0.1062486263580313</v>
-      </c>
-      <c r="AC2">
-        <v>-0.123295039860141</v>
+        <v>0.07746242707851946</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -648,7 +657,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.024</v>
+        <v>-0.016</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -657,28 +666,28 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.0009457755359394705</v>
+        <v>-0.0002528285190569496</v>
       </c>
       <c r="AK2">
-        <v>-0.001439194051331255</v>
+        <v>-0.001067805659369995</v>
       </c>
       <c r="AL2">
-        <v>0.013</v>
+        <v>4.172</v>
       </c>
       <c r="AM2">
-        <v>0.009999999999999998</v>
+        <v>0.7819999999999996</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO2">
-        <v>-46.61538461538461</v>
+        <v>-0.2924256951102589</v>
       </c>
       <c r="AP2">
-        <v>0.06837606837606838</v>
+        <v>-0.004155844155844156</v>
       </c>
       <c r="AQ2">
-        <v>-60.60000000000001</v>
+        <v>-1.560102301790282</v>
       </c>
     </row>
     <row r="3">
@@ -698,7 +707,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-0.019</v>
+        <v>0.042</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -707,7 +716,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -716,37 +725,37 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.024</v>
+        <v>0.016</v>
       </c>
       <c r="V3">
-        <v>0.0009448818897637796</v>
+        <v>0.0005594405594405594</v>
       </c>
       <c r="W3">
-        <v>-0.001061452513966481</v>
+        <v>0.00302158273381295</v>
       </c>
       <c r="X3">
-        <v>0.1062486263580313</v>
+        <v>0.07746242707851946</v>
       </c>
       <c r="Y3">
-        <v>-0.1073100788719978</v>
+        <v>-0.07444084434470651</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.0170464135021097</v>
+        <v>-0.02135642135642135</v>
       </c>
       <c r="AB3">
-        <v>0.1062486263580313</v>
+        <v>0.07746242707851946</v>
       </c>
       <c r="AC3">
-        <v>-0.123295039860141</v>
+        <v>-0.09881884843494081</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -758,7 +767,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.024</v>
+        <v>-0.016</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -767,28 +776,138 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.0009457755359394705</v>
+        <v>-0.0005597537083683179</v>
       </c>
       <c r="AK3">
-        <v>-0.001439194051331255</v>
+        <v>-0.001067805659369995</v>
       </c>
       <c r="AL3">
-        <v>0.013</v>
+        <v>0.002</v>
       </c>
       <c r="AM3">
-        <v>0.009999999999999998</v>
+        <v>0.002</v>
       </c>
       <c r="AN3">
         <v>-0</v>
       </c>
       <c r="AO3">
-        <v>-46.61538461538461</v>
+        <v>-296</v>
       </c>
       <c r="AP3">
-        <v>0.06837606837606838</v>
+        <v>0.04102564102564103</v>
       </c>
       <c r="AQ3">
-        <v>-60.60000000000001</v>
+        <v>-296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bulgartabac Holding AD (BUL:BTH)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Tobacco</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.203</v>
+      </c>
+      <c r="E4">
+        <v>-0.00298</v>
+      </c>
+      <c r="G4">
+        <v>0.0388634280476627</v>
+      </c>
+      <c r="H4">
+        <v>0.0388634280476627</v>
+      </c>
+      <c r="I4">
+        <v>-0.005756186984417965</v>
+      </c>
+      <c r="J4">
+        <v>-0.0052336207005791</v>
+      </c>
+      <c r="K4">
+        <v>19.2</v>
+      </c>
+      <c r="L4">
+        <v>0.1759853345554537</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0.07746242707851946</v>
+      </c>
+      <c r="AB4">
+        <v>0.07746242707851946</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>4.17</v>
+      </c>
+      <c r="AM4">
+        <v>0.7799999999999998</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>-0.150599520383693</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>-0.8051282051282054</v>
       </c>
     </row>
   </sheetData>
